--- a/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación, discapacidad física</t>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,68</t>
+          <t>0,0; 8,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 11,78</t>
+          <t>1,23; 10,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,05</t>
+          <t>0,0; 10,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 13,91</t>
+          <t>2,68; 14,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 11,01</t>
+          <t>1,02; 10,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,89</t>
+          <t>1,23; 12,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 16,3</t>
+          <t>3,97; 16,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,56</t>
+          <t>1,21; 7,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,57</t>
+          <t>1,69; 7,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,8</t>
+          <t>1,34; 8,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 12,49</t>
+          <t>4,36; 12,24</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,51</t>
+          <t>0,9; 3,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,8</t>
+          <t>1,61; 4,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,51</t>
+          <t>0,97; 3,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,92</t>
+          <t>4,03; 8,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,85</t>
+          <t>1,88; 4,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,52</t>
+          <t>2,98; 6,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,94</t>
+          <t>1,22; 4,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,77</t>
+          <t>4,93; 10,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,68</t>
+          <t>1,66; 3,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,15</t>
+          <t>2,65; 5,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,19</t>
+          <t>1,34; 3,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,14</t>
+          <t>4,99; 8,15</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,51</t>
+          <t>0,4; 4,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,46</t>
+          <t>1,72; 8,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,84</t>
+          <t>1,1; 4,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,19</t>
+          <t>2,08; 8,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,9</t>
+          <t>0,42; 3,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,56</t>
+          <t>1,12; 6,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,69</t>
+          <t>1,27; 4,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,05</t>
+          <t>0,44; 3,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,27</t>
+          <t>1,31; 5,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,97</t>
+          <t>1,52; 4,82</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,97</t>
+          <t>0,96; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,25</t>
+          <t>1,76; 4,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,16</t>
+          <t>1,55; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,75</t>
+          <t>3,75; 6,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,87</t>
+          <t>2,24; 4,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,99</t>
+          <t>2,48; 5,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,41</t>
+          <t>1,32; 3,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,44</t>
+          <t>4,59; 8,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,55</t>
+          <t>1,95; 3,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,11</t>
+          <t>2,33; 4,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,3</t>
+          <t>1,72; 3,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,97</t>
+          <t>4,59; 7,01</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con limitación, discapacidad física (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2517</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3747</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2509</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2264</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5179</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3656</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5026</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8926</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4817</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>684; 5979</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4159</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1463; 7956</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>589; 5731</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>636; 6478</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>628; 6188</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2460; 10115</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1301; 7977</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1985; 9382</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1230; 7673</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5088; 14279</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6067</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8787</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6813</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26670</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10797</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15035</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8357</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>35302</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16864</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23822</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15170</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>61971</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2787; 11011</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4898; 14930</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3369; 11417</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18565; 36964</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6636; 17130</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10114; 22481</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4638; 15232</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>25467; 52850</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11030; 24219</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>17103; 32447</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9751; 23025</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>48713; 79641</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5376</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5632</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6697</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7787</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9339</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4217</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>462; 5761</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2344; 11994</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1640; 7306</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2569; 10161</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5072</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>591; 5443</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2058; 12444</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3293; 12075</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1113; 7662</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3619; 14037</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5051; 16030</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13156</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13758</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34124</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18269</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19165</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12645</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>46113</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27217</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32322</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26402</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>80237</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4835; 14749</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8417; 21328</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8157; 21193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24920; 44525</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11828; 25565</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13359; 27717</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7533; 18987</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>34970; 62420</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20139; 37367</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>23632; 41632</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>18841; 36896</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>65556; 99978</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,53</t>
+          <t>0,0; 9,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,78</t>
+          <t>1,3; 10,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,23</t>
+          <t>0,0; 10,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,55</t>
+          <t>2,4; 14,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,16</t>
+          <t>1,16; 11,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,43</t>
+          <t>1,01; 9,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,08</t>
+          <t>1,25; 11,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 16,31</t>
+          <t>3,9; 16,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,4</t>
+          <t>1,18; 7,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,98</t>
+          <t>1,7; 8,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,35</t>
+          <t>1,32; 8,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,24</t>
+          <t>4,04; 12,35</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,55</t>
+          <t>0,88; 3,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,9</t>
+          <t>1,57; 4,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,27</t>
+          <t>0,94; 3,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,03</t>
+          <t>4,17; 7,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,84</t>
+          <t>1,93; 4,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,62</t>
+          <t>2,95; 6,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,01</t>
+          <t>1,19; 3,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,23</t>
+          <t>4,93; 9,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,65</t>
+          <t>1,69; 3,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,03</t>
+          <t>2,59; 5,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,16</t>
+          <t>1,36; 3,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,15</t>
+          <t>5,09; 8,12</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,93</t>
+          <t>0,4; 4,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,82</t>
+          <t>1,9; 8,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,89</t>
+          <t>1,08; 4,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,22</t>
+          <t>2,09; 7,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,89</t>
+          <t>0,43; 3,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,79</t>
+          <t>1,05; 6,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,64</t>
+          <t>1,28; 4,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,02</t>
+          <t>0,4; 3,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,09</t>
+          <t>1,58; 5,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,82</t>
+          <t>1,52; 4,67</t>
         </is>
       </c>
     </row>
@@ -1137,52 +1137,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,93</t>
+          <t>1,0; 2,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,47</t>
+          <t>1,8; 4,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,03</t>
+          <t>1,57; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,7</t>
+          <t>3,91; 6,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,84</t>
+          <t>2,3; 5,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,14</t>
+          <t>2,37; 5,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,33</t>
+          <t>1,28; 3,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,19</t>
+          <t>4,5; 8,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,62</t>
+          <t>1,89; 3,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,1</t>
+          <t>2,39; 4,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,01</t>
+          <t>4,53; 6,92</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4817</t>
+          <t>0; 5170</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>684; 5979</t>
+          <t>719; 5707</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4159</t>
+          <t>0; 4170</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1463; 7956</t>
+          <t>1313; 7884</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>589; 5731</t>
+          <t>595; 5867</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>636; 6478</t>
+          <t>628; 5901</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>628; 6188</t>
+          <t>640; 5970</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2460; 10115</t>
+          <t>2420; 10111</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1301; 7977</t>
+          <t>1277; 7909</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1985; 9382</t>
+          <t>1995; 9605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1230; 7673</t>
+          <t>1210; 7406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5088; 14279</t>
+          <t>4709; 14415</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2787; 11011</t>
+          <t>2744; 11085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4898; 14930</t>
+          <t>4793; 14674</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3369; 11417</t>
+          <t>3286; 12334</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18565; 36964</t>
+          <t>19224; 36461</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6636; 17130</t>
+          <t>6819; 17248</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10114; 22481</t>
+          <t>10013; 21729</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4638; 15232</t>
+          <t>4526; 14793</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25467; 52850</t>
+          <t>25453; 51158</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11030; 24219</t>
+          <t>11207; 24273</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17103; 32447</t>
+          <t>16714; 32767</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9751; 23025</t>
+          <t>9902; 23073</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48713; 79641</t>
+          <t>49770; 79384</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>462; 5761</t>
+          <t>462; 5112</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2344; 11994</t>
+          <t>2589; 11707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1640; 7306</t>
+          <t>1621; 7377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2569; 10161</t>
+          <t>2579; 9573</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 5026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>591; 5443</t>
+          <t>596; 5556</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2058; 12444</t>
+          <t>1925; 11784</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3293; 12075</t>
+          <t>3341; 12089</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1113; 7662</t>
+          <t>1013; 7951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3619; 14037</t>
+          <t>4363; 14872</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5051; 16030</t>
+          <t>5061; 15544</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4835; 14749</t>
+          <t>5012; 15030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8417; 21328</t>
+          <t>8595; 20541</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8157; 21193</t>
+          <t>8253; 21186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24920; 44525</t>
+          <t>26008; 45035</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11828; 25565</t>
+          <t>12140; 26620</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13359; 27717</t>
+          <t>12767; 27542</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7533; 18987</t>
+          <t>7317; 19810</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34970; 62420</t>
+          <t>34286; 61958</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20139; 37367</t>
+          <t>19548; 36688</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23632; 41632</t>
+          <t>24241; 42138</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18841; 36896</t>
+          <t>18841; 36956</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65556; 99978</t>
+          <t>64565; 98776</t>
         </is>
       </c>
     </row>
